--- a/archive/2026-10-26/svod.xlsx
+++ b/archive/2026-10-26/svod.xlsx
@@ -4904,7 +4904,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CG57"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -23951,18 +23951,18 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AD71"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="15" style="0" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="15" style="0" width="16.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28483,7 +28483,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L664"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
